--- a/data/carbon/Bourgneuf2025_Biomass_C_cores.xlsx
+++ b/data/carbon/Bourgneuf2025_Biomass_C_cores.xlsx
@@ -15,6 +15,7 @@
     <sheet name="data" sheetId="2" r:id="rId1"/>
     <sheet name="biomass" sheetId="1" r:id="rId2"/>
     <sheet name="carbon" sheetId="3" r:id="rId3"/>
+    <sheet name="moisture" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">carbon!$A$1:$J$22</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="159">
   <si>
     <t>Station</t>
   </si>
@@ -656,6 +657,39 @@
   <si>
     <t>* Samples not well homogenised</t>
   </si>
+  <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>Initial weight</t>
+  </si>
+  <si>
+    <t>Container weight</t>
+  </si>
+  <si>
+    <t>Total weight with container</t>
+  </si>
+  <si>
+    <t>Total weight after 2 hours</t>
+  </si>
+  <si>
+    <t>Total weight after 3 hours</t>
+  </si>
+  <si>
+    <t>Transferred weight after 3 hours</t>
+  </si>
+  <si>
+    <t>H_05_A</t>
+  </si>
+  <si>
+    <t>H_05_B</t>
+  </si>
+  <si>
+    <t>H_28_A</t>
+  </si>
+  <si>
+    <t>H_28_B</t>
+  </si>
 </sst>
 </file>
 
@@ -663,10 +697,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="169" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,6 +730,7 @@
       <sz val="11"/>
       <color indexed="64"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -768,6 +803,12 @@
       <name val="Cambria"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -977,7 +1018,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -995,13 +1036,80 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="2" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="4" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="2" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="4" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1013,17 +1121,14 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1034,71 +1139,8 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="2" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="2" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="4" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="2" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="4" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="2" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="2" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="4" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="2" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="4" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -7251,1532 +7293,1532 @@
   <dimension ref="A1:J59"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="14" style="11" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="11" customWidth="1"/>
-    <col min="6" max="9" width="14" style="11" customWidth="1"/>
-    <col min="10" max="10" width="17.625" style="11" customWidth="1"/>
-    <col min="11" max="16384" width="10" style="11"/>
+    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="14" style="9" customWidth="1"/>
+    <col min="5" max="5" width="17.625" style="9" customWidth="1"/>
+    <col min="6" max="9" width="14" style="9" customWidth="1"/>
+    <col min="10" max="10" width="17.625" style="9" customWidth="1"/>
+    <col min="11" max="16384" width="10" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="8"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9" t="s">
+      <c r="A1" s="33"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="10"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="10"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="8"/>
     </row>
     <row r="3" spans="1:10" ht="24.75" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="12" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="10"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
     </row>
     <row r="6" spans="1:10" ht="18" customHeight="1">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
     </row>
     <row r="7" spans="1:10" ht="18" customHeight="1">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
     </row>
     <row r="9" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19" t="s">
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="40" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
+      <c r="A12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="28" t="s">
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="31" t="s">
+      <c r="F13" s="17"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="28" t="s">
+      <c r="J13" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="21">
         <v>73.64</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="22">
         <v>1</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="23">
         <v>21.93</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="24">
         <f t="shared" ref="E14:E56" si="0">(D14*1000/B14)*C14</f>
         <v>297.80010863661056</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="25">
         <v>147.38999999999999</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="22">
         <v>1</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="26">
         <v>1.2350000000000001</v>
       </c>
-      <c r="I14" s="39">
+      <c r="I14" s="27">
         <f t="shared" ref="I14" si="1">(H14*1000/F14)*G14</f>
         <v>8.3791301987923212</v>
       </c>
-      <c r="J14" s="36">
+      <c r="J14" s="24">
         <f t="shared" ref="J14" si="2">E14-I14</f>
         <v>289.42097843781823</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="21">
         <v>74.989999999999995</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="22">
         <v>1</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="23">
         <v>23.34</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="24">
         <f t="shared" si="0"/>
         <v>311.24149886651554</v>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="25">
         <v>200.48</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="22">
         <v>1</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15" s="26">
         <v>0.97789999999999999</v>
       </c>
-      <c r="I15" s="39">
+      <c r="I15" s="27">
         <f t="shared" ref="I15" si="3">(H15*1000/F15)*G15</f>
         <v>4.8777932960893855</v>
       </c>
-      <c r="J15" s="36">
+      <c r="J15" s="24">
         <f t="shared" ref="J15" si="4">E15-I15</f>
         <v>306.36370557042613</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="21">
         <v>79.02</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="22">
         <v>1</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="23">
         <v>24.62</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="24">
         <f t="shared" si="0"/>
         <v>311.56669197671476</v>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="25">
         <v>205.94</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="22">
         <v>1</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="26">
         <v>1.3120000000000001</v>
       </c>
-      <c r="I16" s="39">
+      <c r="I16" s="27">
         <f t="shared" ref="I16" si="5">(H16*1000/F16)*G16</f>
         <v>6.3707876080411774</v>
       </c>
-      <c r="J16" s="36">
+      <c r="J16" s="24">
         <f t="shared" ref="J16" si="6">E16-I16</f>
         <v>305.19590436867361</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A17" s="32"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="36"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="24"/>
     </row>
     <row r="18" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="21">
         <v>73.95</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="22">
         <v>1</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="23">
         <v>19.45</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="24">
         <f t="shared" si="0"/>
         <v>263.01555104800542</v>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="25">
         <v>225.17</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="22">
         <v>1</v>
       </c>
-      <c r="H18" s="38">
+      <c r="H18" s="26">
         <v>0.26740000000000003</v>
       </c>
-      <c r="I18" s="39">
+      <c r="I18" s="27">
         <f t="shared" ref="I18:I20" si="7">(H18*1000/F18)*G18</f>
         <v>1.1875471865701472</v>
       </c>
-      <c r="J18" s="36">
+      <c r="J18" s="24">
         <f t="shared" ref="J18:J20" si="8">E18-I18</f>
         <v>261.82800386143526</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="21">
         <v>71.16</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="22">
         <v>1</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="23">
         <v>19.61</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="24">
         <f t="shared" si="0"/>
         <v>275.57616638560989</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="25">
         <v>212.83</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="22">
         <v>1</v>
       </c>
-      <c r="H19" s="38">
+      <c r="H19" s="26">
         <v>0.80649999999999999</v>
       </c>
-      <c r="I19" s="39">
+      <c r="I19" s="27">
         <f t="shared" si="7"/>
         <v>3.7894093877742798</v>
       </c>
-      <c r="J19" s="36">
+      <c r="J19" s="24">
         <f t="shared" si="8"/>
         <v>271.7867569978356</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="21">
         <v>76.31</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="22">
         <v>1</v>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="23">
         <v>21.1</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="24">
         <f t="shared" si="0"/>
         <v>276.5037347660857</v>
       </c>
-      <c r="F20" s="37">
+      <c r="F20" s="25">
         <v>225.05</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="22">
         <v>1</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20" s="26">
         <v>0.35010000000000002</v>
       </c>
-      <c r="I20" s="39">
+      <c r="I20" s="27">
         <f t="shared" si="7"/>
         <v>1.5556542990446567</v>
       </c>
-      <c r="J20" s="36">
+      <c r="J20" s="24">
         <f t="shared" si="8"/>
         <v>274.94808046704105</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A21" s="32"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="36"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="33">
+      <c r="B22" s="21">
         <v>72.75</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="22">
         <v>1</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="23">
         <v>25.56</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="24">
         <f>(D22*1000/B22)*C22</f>
         <v>351.34020618556701</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="25">
         <v>201.84</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="22">
         <v>1</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="26">
         <v>2.1659999999999999</v>
       </c>
-      <c r="I22" s="39">
+      <c r="I22" s="27">
         <f t="shared" ref="I22" si="9">(H22*1000/F22)*G22</f>
         <v>10.73127229488704</v>
       </c>
-      <c r="J22" s="36">
+      <c r="J22" s="24">
         <f t="shared" ref="J22" si="10">E22-I22</f>
         <v>340.60893389067996</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="21">
         <v>76.47</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="22">
         <v>1</v>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="23">
         <v>21.5</v>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="24">
         <f t="shared" si="0"/>
         <v>281.15600889237612</v>
       </c>
-      <c r="F23" s="37">
+      <c r="F23" s="25">
         <v>216.43</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="22">
         <v>1</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23" s="26">
         <v>1.0720000000000001</v>
       </c>
-      <c r="I23" s="39">
+      <c r="I23" s="27">
         <f t="shared" ref="I23:I39" si="11">(H23*1000/F23)*G23</f>
         <v>4.9531026197846879</v>
       </c>
-      <c r="J23" s="36">
+      <c r="J23" s="24">
         <f t="shared" ref="J23:J39" si="12">E23-I23</f>
         <v>276.20290627259141</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="21">
         <v>75.47</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="22">
         <v>1</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="23">
         <v>24.14</v>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="24">
         <f t="shared" si="0"/>
         <v>319.86219689943022</v>
       </c>
-      <c r="F24" s="37">
+      <c r="F24" s="25">
         <v>205.63</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="22">
         <v>1</v>
       </c>
-      <c r="H24" s="38">
+      <c r="H24" s="26">
         <v>1.56</v>
       </c>
-      <c r="I24" s="39">
+      <c r="I24" s="27">
         <f t="shared" si="11"/>
         <v>7.5864416670719255</v>
       </c>
-      <c r="J24" s="36">
+      <c r="J24" s="24">
         <f t="shared" si="12"/>
         <v>312.27575523235828</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="21">
         <v>73.03</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="22">
         <v>1</v>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="23">
         <v>24.03</v>
       </c>
-      <c r="E25" s="36">
+      <c r="E25" s="24">
         <f t="shared" si="0"/>
         <v>329.0428590990004</v>
       </c>
-      <c r="F25" s="37">
+      <c r="F25" s="25">
         <v>202.64</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="22">
         <v>1</v>
       </c>
-      <c r="H25" s="38">
+      <c r="H25" s="26">
         <v>1.196</v>
       </c>
-      <c r="I25" s="39">
+      <c r="I25" s="27">
         <f t="shared" si="11"/>
         <v>5.9020923805763923</v>
       </c>
-      <c r="J25" s="36">
+      <c r="J25" s="24">
         <f t="shared" si="12"/>
         <v>323.140766718424</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="B26" s="33">
+      <c r="B26" s="21">
         <v>72.78</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="22">
         <v>1</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="23">
         <v>23.33</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="24">
         <f t="shared" si="0"/>
         <v>320.55509755427317</v>
       </c>
-      <c r="F26" s="37">
+      <c r="F26" s="25">
         <v>207.4</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="22">
         <v>1</v>
       </c>
-      <c r="H26" s="38">
+      <c r="H26" s="26">
         <v>0.88680000000000003</v>
       </c>
-      <c r="I26" s="39">
+      <c r="I26" s="27">
         <f t="shared" si="11"/>
         <v>4.2757955641272902</v>
       </c>
-      <c r="J26" s="36">
+      <c r="J26" s="24">
         <f t="shared" si="12"/>
         <v>316.27930199014588</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="21">
         <v>73.430000000000007</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="22">
         <v>1</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="23">
         <v>22.67</v>
       </c>
-      <c r="E27" s="36">
+      <c r="E27" s="24">
         <f t="shared" si="0"/>
         <v>308.72940215170911</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="25">
         <v>198.64</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="22">
         <v>1</v>
       </c>
-      <c r="H27" s="38">
+      <c r="H27" s="26">
         <v>0.83509999999999995</v>
       </c>
-      <c r="I27" s="39">
+      <c r="I27" s="27">
         <f t="shared" si="11"/>
         <v>4.2040877970197341</v>
       </c>
-      <c r="J27" s="36">
+      <c r="J27" s="24">
         <f t="shared" si="12"/>
         <v>304.52531435468939</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B28" s="33">
+      <c r="B28" s="21">
         <v>74.959999999999994</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="22">
         <v>1</v>
       </c>
-      <c r="D28" s="35">
+      <c r="D28" s="23">
         <v>23.97</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="24">
         <f t="shared" si="0"/>
         <v>319.77054429028817</v>
       </c>
-      <c r="F28" s="37">
+      <c r="F28" s="25">
         <v>207.59</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="22">
         <v>1</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28" s="26">
         <v>1.4990000000000001</v>
       </c>
-      <c r="I28" s="39">
+      <c r="I28" s="27">
         <f t="shared" si="11"/>
         <v>7.2209644009827061</v>
       </c>
-      <c r="J28" s="36">
+      <c r="J28" s="24">
         <f t="shared" si="12"/>
         <v>312.54957988930545</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A29" s="32"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="36"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="24"/>
     </row>
     <row r="30" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="21">
         <v>73.31</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="22">
         <v>1</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="23">
         <v>23.24</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="24">
         <f t="shared" si="0"/>
         <v>317.00995771381804</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="25">
         <v>209.75</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="22">
         <v>1</v>
       </c>
-      <c r="H30" s="38">
+      <c r="H30" s="26">
         <v>1.0369999999999999</v>
       </c>
-      <c r="I30" s="39">
+      <c r="I30" s="27">
         <f t="shared" si="11"/>
         <v>4.9439809296781885</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="24">
         <f t="shared" si="12"/>
         <v>312.06597678413988</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="21">
         <v>77.77</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="22">
         <v>1</v>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="23">
         <v>24.78</v>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="24">
         <f t="shared" si="0"/>
         <v>318.63186318631864</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="25">
         <v>207.17</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="22">
         <v>1</v>
       </c>
-      <c r="H31" s="38">
+      <c r="H31" s="26">
         <v>0.60340000000000005</v>
       </c>
-      <c r="I31" s="39">
+      <c r="I31" s="27">
         <f t="shared" si="11"/>
         <v>2.9125838683207035</v>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="24">
         <f t="shared" si="12"/>
         <v>315.71927931799792</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="21">
         <v>77.14</v>
       </c>
-      <c r="C32" s="34">
+      <c r="C32" s="22">
         <v>1</v>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="23">
         <v>20.83</v>
       </c>
-      <c r="E32" s="36">
+      <c r="E32" s="24">
         <f t="shared" si="0"/>
         <v>270.02851957479908</v>
       </c>
-      <c r="F32" s="37">
+      <c r="F32" s="25">
         <v>216.79</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="22">
         <v>1</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32" s="26">
         <v>1.5</v>
       </c>
-      <c r="I32" s="39">
+      <c r="I32" s="27">
         <f t="shared" si="11"/>
         <v>6.9191383366391443</v>
       </c>
-      <c r="J32" s="36">
+      <c r="J32" s="24">
         <f t="shared" si="12"/>
         <v>263.10938123815993</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="21">
         <v>71.209999999999994</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="22">
         <v>1</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="23">
         <v>21.72</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="24">
         <f t="shared" si="0"/>
         <v>305.01334082291817</v>
       </c>
-      <c r="F33" s="37">
+      <c r="F33" s="25">
         <v>216.83</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="22">
         <v>1</v>
       </c>
-      <c r="H33" s="38">
+      <c r="H33" s="26">
         <v>1.012</v>
       </c>
-      <c r="I33" s="39">
+      <c r="I33" s="27">
         <f t="shared" si="11"/>
         <v>4.6672508416731997</v>
       </c>
-      <c r="J33" s="36">
+      <c r="J33" s="24">
         <f t="shared" si="12"/>
         <v>300.34608998124497</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="21">
         <v>71.59</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="22">
         <v>1</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="23">
         <v>22.41</v>
       </c>
-      <c r="E34" s="36">
+      <c r="E34" s="24">
         <f t="shared" si="0"/>
         <v>313.0325464450342</v>
       </c>
-      <c r="F34" s="37">
+      <c r="F34" s="25">
         <v>213.69</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="22">
         <v>1</v>
       </c>
-      <c r="H34" s="38">
+      <c r="H34" s="26">
         <v>2.198</v>
       </c>
-      <c r="I34" s="39">
+      <c r="I34" s="27">
         <f t="shared" si="11"/>
         <v>10.285928213767608</v>
       </c>
-      <c r="J34" s="36">
+      <c r="J34" s="24">
         <f t="shared" si="12"/>
         <v>302.74661823126661</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B35" s="33">
+      <c r="B35" s="21">
         <v>70.290000000000006</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="22">
         <v>1</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="23">
         <v>20.53</v>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="24">
         <f t="shared" si="0"/>
         <v>292.07568644188359</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="25">
         <v>177.55</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="22">
         <v>1</v>
       </c>
-      <c r="H35" s="38">
+      <c r="H35" s="26">
         <v>1.4670000000000001</v>
       </c>
-      <c r="I35" s="39">
+      <c r="I35" s="27">
         <f t="shared" si="11"/>
         <v>8.2624612785130935</v>
       </c>
-      <c r="J35" s="36">
+      <c r="J35" s="24">
         <f t="shared" si="12"/>
         <v>283.81322516337048</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A36" s="32" t="s">
+      <c r="A36" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B36" s="33">
+      <c r="B36" s="21">
         <v>72.09</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="22">
         <v>1</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="23">
         <v>21.26</v>
       </c>
-      <c r="E36" s="36">
+      <c r="E36" s="24">
         <f t="shared" si="0"/>
         <v>294.90914135108892</v>
       </c>
-      <c r="F36" s="37">
+      <c r="F36" s="25">
         <v>215.55</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="22">
         <v>1</v>
       </c>
-      <c r="H36" s="38">
+      <c r="H36" s="26">
         <v>1.216</v>
       </c>
-      <c r="I36" s="39">
+      <c r="I36" s="27">
         <f t="shared" si="11"/>
         <v>5.6413825098585013</v>
       </c>
-      <c r="J36" s="36">
+      <c r="J36" s="24">
         <f t="shared" si="12"/>
         <v>289.26775884123043</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A37" s="32"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="36"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="24"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B38" s="33">
+      <c r="B38" s="21">
         <v>71.27</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="22">
         <v>1</v>
       </c>
-      <c r="D38" s="35">
+      <c r="D38" s="23">
         <v>22.7</v>
       </c>
-      <c r="E38" s="36">
+      <c r="E38" s="24">
         <f t="shared" si="0"/>
         <v>318.50708573032131</v>
       </c>
-      <c r="F38" s="37">
+      <c r="F38" s="25">
         <v>202.84</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="22">
         <v>1</v>
       </c>
-      <c r="H38" s="38">
+      <c r="H38" s="26">
         <v>0.92130000000000001</v>
       </c>
-      <c r="I38" s="39">
+      <c r="I38" s="27">
         <f t="shared" si="11"/>
         <v>4.5420035495957398</v>
       </c>
-      <c r="J38" s="36">
+      <c r="J38" s="24">
         <f t="shared" si="12"/>
         <v>313.96508218072557</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B39" s="33">
+      <c r="B39" s="21">
         <v>70.16</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="22">
         <v>1</v>
       </c>
-      <c r="D39" s="35">
+      <c r="D39" s="23">
         <v>20.91</v>
       </c>
-      <c r="E39" s="36">
+      <c r="E39" s="24">
         <f t="shared" si="0"/>
         <v>298.03306727480049</v>
       </c>
-      <c r="F39" s="37">
+      <c r="F39" s="25">
         <v>215.32</v>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="22">
         <v>1</v>
       </c>
-      <c r="H39" s="38">
+      <c r="H39" s="26">
         <v>0.89419999999999999</v>
       </c>
-      <c r="I39" s="39">
+      <c r="I39" s="27">
         <f t="shared" si="11"/>
         <v>4.1528887237599852</v>
       </c>
-      <c r="J39" s="36">
+      <c r="J39" s="24">
         <f t="shared" si="12"/>
         <v>293.8801785510405</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A40" s="32"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="36"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="24"/>
     </row>
     <row r="41" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="B41" s="33">
+      <c r="B41" s="21">
         <v>75.040000000000006</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="22">
         <v>1</v>
       </c>
-      <c r="D41" s="35">
+      <c r="D41" s="23">
         <v>24.56</v>
       </c>
-      <c r="E41" s="36">
+      <c r="E41" s="24">
         <f t="shared" si="0"/>
         <v>327.29211087420038</v>
       </c>
-      <c r="F41" s="37">
+      <c r="F41" s="25">
         <v>211.41</v>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="22">
         <v>1</v>
       </c>
-      <c r="H41" s="38">
+      <c r="H41" s="26">
         <v>2.383</v>
       </c>
-      <c r="I41" s="39">
+      <c r="I41" s="27">
         <f t="shared" ref="I41:I56" si="13">(H41*1000/F41)*G41</f>
         <v>11.271936048436688</v>
       </c>
-      <c r="J41" s="36">
+      <c r="J41" s="24">
         <f t="shared" ref="J41:J56" si="14">E41-I41</f>
         <v>316.02017482576366</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B42" s="33">
+      <c r="B42" s="21">
         <v>70.31</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="22">
         <v>1</v>
       </c>
-      <c r="D42" s="35">
+      <c r="D42" s="23">
         <v>23.55</v>
       </c>
-      <c r="E42" s="36">
+      <c r="E42" s="24">
         <f t="shared" si="0"/>
         <v>334.945242497511</v>
       </c>
-      <c r="F42" s="37">
+      <c r="F42" s="25">
         <v>210.02</v>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="22">
         <v>1</v>
       </c>
-      <c r="H42" s="38">
+      <c r="H42" s="26">
         <v>1.6659999999999999</v>
       </c>
-      <c r="I42" s="39">
+      <c r="I42" s="27">
         <f t="shared" si="13"/>
         <v>7.932577849728597</v>
       </c>
-      <c r="J42" s="36">
+      <c r="J42" s="24">
         <f t="shared" si="14"/>
         <v>327.0126646477824</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="33">
+      <c r="B43" s="21">
         <v>71.94</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="22">
         <v>1</v>
       </c>
-      <c r="D43" s="35">
+      <c r="D43" s="23">
         <v>22.09</v>
       </c>
-      <c r="E43" s="36">
+      <c r="E43" s="24">
         <f t="shared" si="0"/>
         <v>307.06144008896302</v>
       </c>
-      <c r="F43" s="37">
+      <c r="F43" s="25">
         <v>223.67</v>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="22">
         <v>1</v>
       </c>
-      <c r="H43" s="38">
+      <c r="H43" s="26">
         <v>2.2429999999999999</v>
       </c>
-      <c r="I43" s="39">
+      <c r="I43" s="27">
         <f t="shared" si="13"/>
         <v>10.02816649528323</v>
       </c>
-      <c r="J43" s="36">
+      <c r="J43" s="24">
         <f t="shared" si="14"/>
         <v>297.03327359367978</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B44" s="33">
+      <c r="B44" s="21">
         <v>70.89</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="22">
         <v>1</v>
       </c>
-      <c r="D44" s="35">
+      <c r="D44" s="23">
         <v>22.12</v>
       </c>
-      <c r="E44" s="36">
+      <c r="E44" s="24">
         <f t="shared" si="0"/>
         <v>312.03272675976865</v>
       </c>
-      <c r="F44" s="37">
+      <c r="F44" s="25">
         <v>203.93</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="22">
         <v>1</v>
       </c>
-      <c r="H44" s="38">
+      <c r="H44" s="26">
         <v>1.819</v>
       </c>
-      <c r="I44" s="39">
+      <c r="I44" s="27">
         <f t="shared" si="13"/>
         <v>8.9197273574265683</v>
       </c>
-      <c r="J44" s="36">
+      <c r="J44" s="24">
         <f t="shared" si="14"/>
         <v>303.1129994023421</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="33">
+      <c r="B45" s="21">
         <v>70.510000000000005</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="22">
         <v>1</v>
       </c>
-      <c r="D45" s="35">
+      <c r="D45" s="23">
         <v>22.8</v>
       </c>
-      <c r="E45" s="36">
+      <c r="E45" s="24">
         <f t="shared" si="0"/>
         <v>323.35838888100977</v>
       </c>
-      <c r="F45" s="40">
+      <c r="F45" s="28">
         <v>168.07</v>
       </c>
-      <c r="G45" s="41">
+      <c r="G45" s="29">
         <v>1</v>
       </c>
-      <c r="H45" s="42">
+      <c r="H45" s="30">
         <v>1.218</v>
       </c>
-      <c r="I45" s="39">
+      <c r="I45" s="27">
         <f t="shared" si="13"/>
         <v>7.2469804248229908</v>
       </c>
-      <c r="J45" s="36">
+      <c r="J45" s="24">
         <f t="shared" si="14"/>
         <v>316.11140845618678</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A46" s="32" t="s">
+      <c r="A46" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B46" s="33">
+      <c r="B46" s="21">
         <v>70.349999999999994</v>
       </c>
-      <c r="C46" s="34">
+      <c r="C46" s="22">
         <v>1</v>
       </c>
-      <c r="D46" s="35">
+      <c r="D46" s="23">
         <v>22.09</v>
       </c>
-      <c r="E46" s="36">
+      <c r="E46" s="24">
         <f t="shared" si="0"/>
         <v>314.00142146410803</v>
       </c>
-      <c r="F46" s="37">
+      <c r="F46" s="25">
         <v>239.05</v>
       </c>
-      <c r="G46" s="34">
+      <c r="G46" s="22">
         <v>1</v>
       </c>
-      <c r="H46" s="38">
+      <c r="H46" s="26">
         <v>2.0960000000000001</v>
       </c>
-      <c r="I46" s="39">
+      <c r="I46" s="27">
         <f t="shared" si="13"/>
         <v>8.7680401589625596</v>
       </c>
-      <c r="J46" s="36">
+      <c r="J46" s="24">
         <f t="shared" si="14"/>
         <v>305.23338130514549</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A47" s="32"/>
-      <c r="B47" s="33"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="39"/>
-      <c r="J47" s="36"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="24"/>
     </row>
     <row r="48" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A48" s="32" t="s">
+      <c r="A48" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B48" s="33">
+      <c r="B48" s="21">
         <v>76.97</v>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="22">
         <v>1</v>
       </c>
-      <c r="D48" s="35">
+      <c r="D48" s="23">
         <v>23.84</v>
       </c>
-      <c r="E48" s="36">
+      <c r="E48" s="24">
         <f t="shared" si="0"/>
         <v>309.73106405092892</v>
       </c>
-      <c r="F48" s="37">
+      <c r="F48" s="25">
         <v>232.5</v>
       </c>
-      <c r="G48" s="34">
+      <c r="G48" s="22">
         <v>1</v>
       </c>
-      <c r="H48" s="38">
+      <c r="H48" s="26">
         <v>1.31</v>
       </c>
-      <c r="I48" s="39">
+      <c r="I48" s="27">
         <f t="shared" si="13"/>
         <v>5.634408602150538</v>
       </c>
-      <c r="J48" s="36">
+      <c r="J48" s="24">
         <f t="shared" si="14"/>
         <v>304.09665544877839</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A49" s="32" t="s">
+      <c r="A49" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="33">
+      <c r="B49" s="21">
         <v>70.38</v>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="22">
         <v>1</v>
       </c>
-      <c r="D49" s="35">
+      <c r="D49" s="23">
         <v>23.85</v>
       </c>
-      <c r="E49" s="36">
+      <c r="E49" s="24">
         <f t="shared" si="0"/>
         <v>338.87468030690542</v>
       </c>
-      <c r="F49" s="37">
+      <c r="F49" s="25">
         <v>203.46</v>
       </c>
-      <c r="G49" s="34">
+      <c r="G49" s="22">
         <v>1</v>
       </c>
-      <c r="H49" s="38">
+      <c r="H49" s="26">
         <v>1.367</v>
       </c>
-      <c r="I49" s="39">
+      <c r="I49" s="27">
         <f t="shared" si="13"/>
         <v>6.7187653592843803</v>
       </c>
-      <c r="J49" s="36">
+      <c r="J49" s="24">
         <f t="shared" si="14"/>
         <v>332.15591494762106</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="B50" s="33">
+      <c r="B50" s="21">
         <v>70.27</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="22">
         <v>1</v>
       </c>
-      <c r="D50" s="35">
+      <c r="D50" s="23">
         <v>21.12</v>
       </c>
-      <c r="E50" s="36">
+      <c r="E50" s="24">
         <f t="shared" si="0"/>
         <v>300.55500213462363</v>
       </c>
-      <c r="F50" s="37">
+      <c r="F50" s="25">
         <v>219.48</v>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="22">
         <v>1</v>
       </c>
-      <c r="H50" s="38">
+      <c r="H50" s="26">
         <v>0.95740000000000003</v>
       </c>
-      <c r="I50" s="39">
+      <c r="I50" s="27">
         <f t="shared" si="13"/>
         <v>4.3621286677601603</v>
       </c>
-      <c r="J50" s="36">
+      <c r="J50" s="24">
         <f t="shared" si="14"/>
         <v>296.19287346686349</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A51" s="32" t="s">
+      <c r="A51" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="B51" s="33">
+      <c r="B51" s="21">
         <v>73.98</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="22">
         <v>1</v>
       </c>
-      <c r="D51" s="35">
+      <c r="D51" s="23">
         <v>23.35</v>
       </c>
-      <c r="E51" s="36">
+      <c r="E51" s="24">
         <f t="shared" si="0"/>
         <v>315.6258448229251</v>
       </c>
-      <c r="F51" s="37">
+      <c r="F51" s="25">
         <v>205.09</v>
       </c>
-      <c r="G51" s="34">
+      <c r="G51" s="22">
         <v>1</v>
       </c>
-      <c r="H51" s="38">
+      <c r="H51" s="26">
         <v>1.321</v>
       </c>
-      <c r="I51" s="39">
+      <c r="I51" s="27">
         <f t="shared" si="13"/>
         <v>6.4410746501535909</v>
       </c>
-      <c r="J51" s="36">
+      <c r="J51" s="24">
         <f t="shared" si="14"/>
         <v>309.18477017277149</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A52" s="32" t="s">
+      <c r="A52" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B52" s="33">
+      <c r="B52" s="21">
         <v>70.260000000000005</v>
       </c>
-      <c r="C52" s="34">
+      <c r="C52" s="22">
         <v>1</v>
       </c>
-      <c r="D52" s="35">
+      <c r="D52" s="23">
         <v>17.899999999999999</v>
       </c>
-      <c r="E52" s="36">
+      <c r="E52" s="24">
         <f t="shared" si="0"/>
         <v>254.7680045545118</v>
       </c>
-      <c r="F52" s="37">
+      <c r="F52" s="25">
         <v>230.36</v>
       </c>
-      <c r="G52" s="34">
+      <c r="G52" s="22">
         <v>1</v>
       </c>
-      <c r="H52" s="38">
+      <c r="H52" s="26">
         <v>1.286</v>
       </c>
-      <c r="I52" s="39">
+      <c r="I52" s="27">
         <f t="shared" si="13"/>
         <v>5.582566417780864</v>
       </c>
-      <c r="J52" s="36">
+      <c r="J52" s="24">
         <f t="shared" si="14"/>
         <v>249.18543813673094</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A53" s="32" t="s">
+      <c r="A53" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B53" s="33">
+      <c r="B53" s="21">
         <v>73.5</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="22">
         <v>1</v>
       </c>
-      <c r="D53" s="35">
+      <c r="D53" s="23">
         <v>22.03</v>
       </c>
-      <c r="E53" s="36">
+      <c r="E53" s="24">
         <f t="shared" si="0"/>
         <v>299.72789115646259</v>
       </c>
-      <c r="F53" s="37">
+      <c r="F53" s="25">
         <v>221.33</v>
       </c>
-      <c r="G53" s="34">
+      <c r="G53" s="22">
         <v>1</v>
       </c>
-      <c r="H53" s="38">
+      <c r="H53" s="26">
         <v>1.794</v>
       </c>
-      <c r="I53" s="39">
+      <c r="I53" s="27">
         <f t="shared" si="13"/>
         <v>8.1055437581891283</v>
       </c>
-      <c r="J53" s="36">
+      <c r="J53" s="24">
         <f t="shared" si="14"/>
         <v>291.62234739827346</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A54" s="32"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="36"/>
+      <c r="A54" s="20"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="27"/>
+      <c r="J54" s="24"/>
     </row>
     <row r="55" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A55" s="32" t="s">
+      <c r="A55" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="B55" s="33">
+      <c r="B55" s="21">
         <v>72.209999999999994</v>
       </c>
-      <c r="C55" s="34">
+      <c r="C55" s="22">
         <v>1</v>
       </c>
-      <c r="D55" s="35">
+      <c r="D55" s="23">
         <v>23.34</v>
       </c>
-      <c r="E55" s="36">
+      <c r="E55" s="24">
         <f t="shared" si="0"/>
         <v>323.22393020357293</v>
       </c>
-      <c r="F55" s="37">
+      <c r="F55" s="25">
         <v>205.55</v>
       </c>
-      <c r="G55" s="34">
+      <c r="G55" s="22">
         <v>1</v>
       </c>
-      <c r="H55" s="38">
+      <c r="H55" s="26">
         <v>1.55</v>
       </c>
-      <c r="I55" s="39">
+      <c r="I55" s="27">
         <f t="shared" si="13"/>
         <v>7.540744344441741</v>
       </c>
-      <c r="J55" s="36">
+      <c r="J55" s="24">
         <f t="shared" si="14"/>
         <v>315.68318585913119</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A56" s="32" t="s">
+      <c r="A56" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B56" s="33">
+      <c r="B56" s="21">
         <v>75.84</v>
       </c>
-      <c r="C56" s="34">
+      <c r="C56" s="22">
         <v>1</v>
       </c>
-      <c r="D56" s="35">
+      <c r="D56" s="23">
         <v>20.21</v>
       </c>
-      <c r="E56" s="36">
+      <c r="E56" s="24">
         <f t="shared" si="0"/>
         <v>266.48206751054852</v>
       </c>
-      <c r="F56" s="37">
+      <c r="F56" s="25">
         <v>204.62</v>
       </c>
-      <c r="G56" s="34">
+      <c r="G56" s="22">
         <v>1</v>
       </c>
-      <c r="H56" s="38">
+      <c r="H56" s="26">
         <v>0.71430000000000005</v>
       </c>
-      <c r="I56" s="39">
+      <c r="I56" s="27">
         <f t="shared" si="13"/>
         <v>3.4908611083960515</v>
       </c>
-      <c r="J56" s="36">
+      <c r="J56" s="24">
         <f t="shared" si="14"/>
         <v>262.99120640215244</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A57" s="32"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="34"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="34"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="39"/>
-      <c r="J57" s="36"/>
+      <c r="A57" s="20"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="27"/>
+      <c r="J57" s="24"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="43" t="s">
+      <c r="A59" s="31" t="s">
         <v>147</v>
       </c>
     </row>
@@ -8811,4 +8853,226 @@
   <pageSetup paperSize="9" scale="81" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7.375" customWidth="1"/>
+    <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="20.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15">
+      <c r="A1" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15">
+      <c r="A2" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="32">
+        <v>194.81</v>
+      </c>
+      <c r="E2" s="32">
+        <v>19618.240000000002</v>
+      </c>
+      <c r="F2" s="32">
+        <v>19814.36</v>
+      </c>
+      <c r="G2" s="32">
+        <v>19798.97</v>
+      </c>
+      <c r="H2" s="32">
+        <v>19797.47</v>
+      </c>
+      <c r="I2" s="32">
+        <v>179.56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="32">
+        <v>558.64</v>
+      </c>
+      <c r="E3" s="32">
+        <v>23586.880000000001</v>
+      </c>
+      <c r="F3" s="32">
+        <v>24146.31</v>
+      </c>
+      <c r="G3" s="32">
+        <v>24115.88</v>
+      </c>
+      <c r="H3" s="32">
+        <v>24116.32</v>
+      </c>
+      <c r="I3" s="32">
+        <v>529.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
+      <c r="A4" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="32">
+        <v>500.84</v>
+      </c>
+      <c r="E4" s="32">
+        <v>19819.91</v>
+      </c>
+      <c r="F4" s="32">
+        <v>20322.28</v>
+      </c>
+      <c r="G4" s="32">
+        <v>20296.41</v>
+      </c>
+      <c r="H4" s="32">
+        <v>20299.439999999999</v>
+      </c>
+      <c r="I4" s="32">
+        <v>478.03</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="32">
+        <v>1320.55</v>
+      </c>
+      <c r="E5" s="32">
+        <v>21275.31</v>
+      </c>
+      <c r="F5" s="32">
+        <v>22596.57</v>
+      </c>
+      <c r="G5" s="32">
+        <v>22527.67</v>
+      </c>
+      <c r="H5" s="32">
+        <v>22530.09</v>
+      </c>
+      <c r="I5" s="32">
+        <v>1252.26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="A6" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="32">
+        <v>494.47</v>
+      </c>
+      <c r="E6" s="32">
+        <v>20944.669999999998</v>
+      </c>
+      <c r="F6" s="32">
+        <v>21439.69</v>
+      </c>
+      <c r="G6" s="32">
+        <v>21407.26</v>
+      </c>
+      <c r="H6" s="32">
+        <v>21411.88</v>
+      </c>
+      <c r="I6" s="32">
+        <v>467.43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15">
+      <c r="A7" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="32">
+        <v>708.99</v>
+      </c>
+      <c r="E7" s="32">
+        <v>22926.880000000001</v>
+      </c>
+      <c r="F7" s="32">
+        <v>23636.080000000002</v>
+      </c>
+      <c r="G7" s="32">
+        <v>23596.43</v>
+      </c>
+      <c r="H7" s="32">
+        <v>23600.26</v>
+      </c>
+      <c r="I7" s="32">
+        <v>672.06</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>